--- a/tame_output/ON/bt/strategyON_20231208.xlsx
+++ b/tame_output/ON/bt/strategyON_20231208.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.6%</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255679</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227612</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571589</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708493</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066011</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.08750545129302</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239773</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003008</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.13555534016786</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216941</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454037</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780866</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537929</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597765</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527684</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844643</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373819</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502546</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728029</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702053</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487808</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.15777720152482</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.1572943800687</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583693</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742723</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589523</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872956</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946328</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,22 +43025,22 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>2.956315987900167</v>
+        <v>2.956315987900168</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.9272708525580455</v>
+        <v>0.9278213093411022</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.465373314167488</v>
+        <v>3.465593496880711</v>
       </c>
       <c r="F1805" t="n">
-        <v>1.466314672191272</v>
+        <v>1.466865128974329</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.974610200772781</v>
+        <v>3.974940474842615</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231208.xlsx
+++ b/tame_output/ON/bt/strategyON_20231208.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.8%</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-62.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.9278213093411022</v>
+        <v>0.9263972353401487</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.465593496880711</v>
+        <v>3.465023867280329</v>
       </c>
       <c r="F1805" t="n">
-        <v>1.466865128974329</v>
+        <v>1.465441054973375</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.974940474842615</v>
+        <v>3.974086030442043</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231208.xlsx
+++ b/tame_output/ON/bt/strategyON_20231208.xlsx
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>510.8%</t>
+          <t>498.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,27 +1145,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,32 +1293,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>27.0%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>29.8%</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>37.9%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>31.0%</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-62.7%</t>
+          <t>-92.4%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-31.5%</t>
         </is>
       </c>
     </row>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255679</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227612</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571589</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708493</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968023</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066011</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.08750545129302</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239773</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003009</v>
+        <v>3.128298755003008</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.13555534016786</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216941</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454037</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780866</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537929</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597765</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527684</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844643</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.12341686637382</v>
+        <v>3.123416866373819</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502546</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728029</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702053</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487809</v>
+        <v>3.146053372487808</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.15777720152482</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.1572943800687</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083875</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097097</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583693</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872956</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.312164595946328</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,22 +43025,22 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>2.956315987900168</v>
+        <v>2.956315987900167</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.9263972353401487</v>
+        <v>0.6292033611284725</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.465023867280329</v>
+        <v>3.346146317595659</v>
       </c>
       <c r="F1805" t="n">
-        <v>1.465441054973375</v>
+        <v>1.168247180761699</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.974086030442043</v>
+        <v>3.795769705915037</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231208.xlsx
+++ b/tame_output/ON/bt/strategyON_20231208.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-231.7%</t>
+          <t>-268.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.2%</t>
+          <t>481.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-84.6%</t>
+          <t>-109.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-87.4%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,15 +1107,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-96.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-11.0%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,32 +1293,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-92.4%</t>
+          <t>-63.2%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>101.5%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-13.9%</t>
         </is>
       </c>
     </row>
@@ -41904,10 +41904,10 @@
         <v>2.969006534107256</v>
       </c>
       <c r="D1756" t="n">
-        <v>-0.7177734718318018</v>
+        <v>-1.088726551543637</v>
       </c>
       <c r="E1756" t="n">
-        <v>2.681540721060788</v>
+        <v>2.533159489176054</v>
       </c>
       <c r="F1756" t="n">
         <v>1.04617033602595</v>
@@ -41927,10 +41927,10 @@
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>-0.7096563318741567</v>
+        <v>-1.080609411585992</v>
       </c>
       <c r="E1757" t="n">
-        <v>2.684328823581027</v>
+        <v>2.535947591696293</v>
       </c>
       <c r="F1757" t="n">
         <v>1.04617033602595</v>
@@ -41950,10 +41950,10 @@
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>-0.7051469836483715</v>
+        <v>-1.076100063360206</v>
       </c>
       <c r="E1758" t="n">
-        <v>2.682731647501707</v>
+        <v>2.534350415616973</v>
       </c>
       <c r="F1758" t="n">
         <v>1.04617033602595</v>
@@ -41973,10 +41973,10 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>-0.7154541093058067</v>
+        <v>-1.086407189017642</v>
       </c>
       <c r="E1759" t="n">
-        <v>2.678150983339857</v>
+        <v>2.529769751455123</v>
       </c>
       <c r="F1759" t="n">
         <v>1.039171953711096</v>
@@ -41996,10 +41996,10 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>-0.7636967581915186</v>
+        <v>-1.134649837903354</v>
       </c>
       <c r="E1760" t="n">
-        <v>2.68663958174375</v>
+        <v>2.538258349859016</v>
       </c>
       <c r="F1760" t="n">
         <v>1.039171953711096</v>
@@ -42019,10 +42019,10 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>-0.7565987572240169</v>
+        <v>-1.127551836935852</v>
       </c>
       <c r="E1761" t="n">
-        <v>2.70725349117221</v>
+        <v>2.558872259287476</v>
       </c>
       <c r="F1761" t="n">
         <v>1.039279151822472</v>
@@ -42042,10 +42042,10 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-0.7553956909279105</v>
+        <v>-1.126348770639745</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.708208277371694</v>
+        <v>2.559827045486959</v>
       </c>
       <c r="F1762" t="n">
         <v>1.039279151822472</v>
@@ -42065,10 +42065,10 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-0.753042643594665</v>
+        <v>-1.1239957233065</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.714488868441889</v>
+        <v>2.566107636557155</v>
       </c>
       <c r="F1763" t="n">
         <v>1.041632199155718</v>
@@ -42088,10 +42088,10 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-0.7519263616034388</v>
+        <v>-1.122879441315274</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.729512406074429</v>
+        <v>2.581131174189695</v>
       </c>
       <c r="F1764" t="n">
         <v>1.042748481146944</v>
@@ -42111,10 +42111,10 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-0.7481884055423834</v>
+        <v>-1.119141485254219</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.730932569362498</v>
+        <v>2.582551337477764</v>
       </c>
       <c r="F1765" t="n">
         <v>1.045124933427569</v>
@@ -42134,10 +42134,10 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-0.7396912598812502</v>
+        <v>-1.110644339593086</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.732646852125046</v>
+        <v>2.584265620240312</v>
       </c>
       <c r="F1766" t="n">
         <v>1.045124933427569</v>
@@ -42157,10 +42157,10 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-0.7393832997965255</v>
+        <v>-1.110336379508361</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.737158611839782</v>
+        <v>2.588777379955048</v>
       </c>
       <c r="F1767" t="n">
         <v>1.046306647520268</v>
@@ -42180,10 +42180,10 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-0.7376015374259342</v>
+        <v>-1.10855461713777</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.739531613964893</v>
+        <v>2.591150382080159</v>
       </c>
       <c r="F1768" t="n">
         <v>1.046306647520268</v>
@@ -42203,10 +42203,10 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-0.7416788925630255</v>
+        <v>-1.112631972274861</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.752934842173747</v>
+        <v>2.604553610289012</v>
       </c>
       <c r="F1769" t="n">
         <v>1.046306647520268</v>
@@ -42226,10 +42226,10 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-0.7316868116366164</v>
+        <v>-1.102639891348452</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.755246109208444</v>
+        <v>2.606864877323709</v>
       </c>
       <c r="F1770" t="n">
         <v>1.056298728446678</v>
@@ -42249,10 +42249,10 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-0.7322425666926542</v>
+        <v>-1.10319564640449</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.757925617082619</v>
+        <v>2.609544385197885</v>
       </c>
       <c r="F1771" t="n">
         <v>1.0546913146856</v>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-0.7354569191059657</v>
+        <v>-1.106409998817801</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.762164865256442</v>
+        <v>2.613783633371708</v>
       </c>
       <c r="F1772" t="n">
         <v>1.0546913146856</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-0.7524651645085751</v>
+        <v>-1.123418244220411</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.756439139733129</v>
+        <v>2.608057907848395</v>
       </c>
       <c r="F1773" t="n">
         <v>1.057690449698574</v>
@@ -42318,10 +42318,10 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-0.7335054420572206</v>
+        <v>-1.104458521769056</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.764772890884944</v>
+        <v>2.61639165900021</v>
       </c>
       <c r="F1774" t="n">
         <v>1.057690449698574</v>
@@ -42341,10 +42341,10 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-0.7322707174544119</v>
+        <v>-1.103223797166247</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.763502378189649</v>
+        <v>2.615121146304915</v>
       </c>
       <c r="F1775" t="n">
         <v>1.057690449698574</v>
@@ -42364,10 +42364,10 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-0.7423049812780605</v>
+        <v>-1.113258060989896</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.763056282497051</v>
+        <v>2.614675050612317</v>
       </c>
       <c r="F1776" t="n">
         <v>1.057690449698574</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-0.7473439795759274</v>
+        <v>-1.118297059287762</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.785022645067513</v>
+        <v>2.636641413182779</v>
       </c>
       <c r="F1777" t="n">
         <v>1.052651451400707</v>
@@ -42410,10 +42410,10 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-0.7375242614153766</v>
+        <v>-1.108477341127212</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.786419243818963</v>
+        <v>2.638038011934229</v>
       </c>
       <c r="F1778" t="n">
         <v>1.059081391617394</v>
@@ -42433,10 +42433,10 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-0.7357226345764227</v>
+        <v>-1.106675714288258</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.772388456558171</v>
+        <v>2.624007224673437</v>
       </c>
       <c r="F1779" t="n">
         <v>1.059081391617394</v>
@@ -42456,10 +42456,10 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-0.734733952832255</v>
+        <v>-1.10568703254409</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.77089768557151</v>
+        <v>2.622516453686776</v>
       </c>
       <c r="F1780" t="n">
         <v>1.059081391617394</v>
@@ -42479,10 +42479,10 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-0.7267375983107164</v>
+        <v>-1.097690678022551</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.776069853835966</v>
+        <v>2.627688621951231</v>
       </c>
       <c r="F1781" t="n">
         <v>1.067077746138933</v>
@@ -42502,10 +42502,10 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-0.7217538476388077</v>
+        <v>-1.092706927350642</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.789901934695641</v>
+        <v>2.641520702810907</v>
       </c>
       <c r="F1782" t="n">
         <v>1.072061496810842</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-0.7153677086892521</v>
+        <v>-1.086320788401087</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.799184593287252</v>
+        <v>2.650803361402518</v>
       </c>
       <c r="F1783" t="n">
         <v>1.072061496810842</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-0.7271730590078848</v>
+        <v>-1.09812613871972</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.798478541919341</v>
+        <v>2.650097310034607</v>
       </c>
       <c r="F1784" t="n">
         <v>1.060256146492209</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-0.7184412482292185</v>
+        <v>-1.089394327941053</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.807918723840697</v>
+        <v>2.659537491955963</v>
       </c>
       <c r="F1785" t="n">
         <v>1.068987957270875</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-0.7121043615847665</v>
+        <v>-1.083057441296601</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.805764297446463</v>
+        <v>2.657383065561729</v>
       </c>
       <c r="F1786" t="n">
         <v>1.068987957270875</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-0.7095699138573982</v>
+        <v>-1.080522993569233</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.816740734339604</v>
+        <v>2.668359502454871</v>
       </c>
       <c r="F1787" t="n">
         <v>1.068987957270875</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-0.7096458128380028</v>
+        <v>-1.080598892549838</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.809125054940273</v>
+        <v>2.660743823055538</v>
       </c>
       <c r="F1788" t="n">
         <v>1.069751217960202</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-0.7201480023973494</v>
+        <v>-1.091101082109184</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.782688754906907</v>
+        <v>2.634307523022173</v>
       </c>
       <c r="F1789" t="n">
         <v>1.059249028400855</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-0.7219812650764658</v>
+        <v>-1.0929343447883</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.782656289681382</v>
+        <v>2.634275057796649</v>
       </c>
       <c r="F1790" t="n">
         <v>1.059249028400855</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-0.7269903801380497</v>
+        <v>-1.097943459849885</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.781169723485608</v>
+        <v>2.632788491600874</v>
       </c>
       <c r="F1791" t="n">
         <v>1.058254450842321</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-0.7306959367748643</v>
+        <v>-1.101649016486699</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.778915226071248</v>
+        <v>2.630533994186514</v>
       </c>
       <c r="F1792" t="n">
         <v>1.056384775584686</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-0.7294636114174988</v>
+        <v>-1.100416691129334</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.779828008276513</v>
+        <v>2.631446776391779</v>
       </c>
       <c r="F1793" t="n">
         <v>1.057015151956723</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-0.7191356144016466</v>
+        <v>-1.090088694113481</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.788089115247067</v>
+        <v>2.639707883362334</v>
       </c>
       <c r="F1794" t="n">
         <v>1.067343148972576</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-0.7190192792540909</v>
+        <v>-1.089972358965926</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.794656309507926</v>
+        <v>2.646275077623192</v>
       </c>
       <c r="F1795" t="n">
         <v>1.067459484120131</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-0.7208646888309584</v>
+        <v>-1.091817768542793</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.790892116122567</v>
+        <v>2.642510884237834</v>
       </c>
       <c r="F1796" t="n">
         <v>1.067459484120131</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-0.7193662563058596</v>
+        <v>-1.090319336017694</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.79142977699374</v>
+        <v>2.643048545109007</v>
       </c>
       <c r="F1797" t="n">
         <v>1.06895791664523</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-0.7274305084985935</v>
+        <v>-1.098383588210428</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.789482054059959</v>
+        <v>2.641100822175225</v>
       </c>
       <c r="F1798" t="n">
         <v>1.060893664452496</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-0.7287604759598059</v>
+        <v>-1.099713555671641</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.788950067075474</v>
+        <v>2.64056883519074</v>
       </c>
       <c r="F1799" t="n">
         <v>1.060893664452496</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-0.5008957932262947</v>
+        <v>-0.8718488729381295</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.88231241327604</v>
+        <v>2.733931181391306</v>
       </c>
       <c r="F1800" t="n">
         <v>1.060893664452496</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-0.2527942293590779</v>
+        <v>-0.6237473090709127</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.989087635168019</v>
+        <v>2.840706403283285</v>
       </c>
       <c r="F1801" t="n">
         <v>1.060893664452496</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>0.04404417003425243</v>
+        <v>-0.3269089096775823</v>
       </c>
       <c r="E1802" t="n">
-        <v>3.109246005898809</v>
+        <v>2.960864774014075</v>
       </c>
       <c r="F1802" t="n">
         <v>1.175748152933624</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>0.347683726859689</v>
+        <v>-0.02326935285214582</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.23237890309467</v>
+        <v>3.083997671209936</v>
       </c>
       <c r="F1803" t="n">
         <v>1.175748152933624</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>0.6367043333003976</v>
+        <v>0.2657512535885628</v>
       </c>
       <c r="E1804" t="n">
-        <v>3.343926567120411</v>
+        <v>3.195545335235677</v>
       </c>
       <c r="F1804" t="n">
         <v>1.175748152933624</v>
@@ -43025,22 +43025,22 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>2.956315987900167</v>
+        <v>2.965271102466769</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>0.6292033611284725</v>
+        <v>0.5504711808524599</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.346146317595659</v>
+        <v>3.314653445485253</v>
       </c>
       <c r="F1805" t="n">
-        <v>1.168247180761699</v>
+        <v>1.460468080197521</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.795769705915037</v>
+        <v>3.971102245576531</v>
       </c>
     </row>
   </sheetData>
